--- a/data/trans_orig/IP22D6_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D6_2023-Estudios-trans_orig.xlsx
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>34308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62449</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>44171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96615</t>
+          <t>96787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D6_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D6_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5658</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33834</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32193</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29373</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26197</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>28988</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25654</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>29862</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36341</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>34308</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36860</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>88</t>
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>65714</t>
+          <t>62822</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>59748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1289,107 +1289,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4014</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4208</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,29%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4334</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2552</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2765</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,64 +1632,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10754</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,74 +2088,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46065</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>47328</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>44171</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>42157</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>39330</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>91,4%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>52753</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>50370</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53272</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>125</t>
@@ -2163,27 +2163,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>100081</t>
+          <t>90207</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96787</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3701</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4295</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2314,107 +2314,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
